--- a/data/bryan/inputs/bryan_41_plus7or8.xlsx
+++ b/data/bryan/inputs/bryan_41_plus7or8.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\bryan\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C794F024-5E50-4EBC-83CF-A8F8C53A92E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40ECF60-E5F3-46A1-8136-DF0383D8D7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="525" windowWidth="28365" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="23505" windowHeight="12930" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
-    <sheet name="bryan_41_plus7or8" sheetId="1" r:id="rId2"/>
+    <sheet name="bryan_41_plus7or8_wSNE" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>B</t>
   </si>
@@ -93,12 +93,6 @@
     <t>Bryan</t>
   </si>
   <si>
-    <t>Bryan 4,1 (+7) and 4,1b (+8) after i12 punish with no hit confirm</t>
-  </si>
-  <si>
-    <t>Bryan 4,1 (+7) or 4,1b (+8)</t>
-  </si>
-  <si>
     <t>b4</t>
   </si>
   <si>
@@ -133,13 +127,25 @@
   </si>
   <si>
     <t>1+2</t>
+  </si>
+  <si>
+    <t>SSL~b</t>
+  </si>
+  <si>
+    <t>SSR~b</t>
+  </si>
+  <si>
+    <t>Bryan 4,1 (+7) and 4,1b (+8) after i12 punish with no hit confirm (w/snake eyes)</t>
+  </si>
+  <si>
+    <t>Bryan 4,1 (+7) or 4,1b (+8) SNE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,15 +160,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -172,11 +171,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -189,12 +183,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -203,14 +196,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -563,7 +554,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -582,12 +573,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -597,7 +588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B9BB04-D3D2-4E07-A007-5B16E4AB0AD8}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -616,7 +607,7 @@
     <col min="14" max="14" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -636,22 +627,28 @@
         <v>11</v>
       </c>
       <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -664,8 +661,35 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>77</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>30</v>
+      </c>
+      <c r="L2">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -678,10 +702,37 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>-8</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-20</v>
+      </c>
+      <c r="L3">
+        <v>-64</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -689,13 +740,40 @@
       <c r="C4">
         <v>-74</v>
       </c>
-      <c r="D4" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>-5</v>
+      </c>
+      <c r="F4">
+        <v>70</v>
+      </c>
+      <c r="G4">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>22</v>
+      </c>
+      <c r="I4">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>22</v>
+      </c>
+      <c r="K4">
+        <v>70</v>
+      </c>
+      <c r="L4">
+        <v>70</v>
+      </c>
+      <c r="M4">
+        <v>-74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -706,10 +784,37 @@
       <c r="D5">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-4</v>
+      </c>
+      <c r="L5">
+        <v>19</v>
+      </c>
+      <c r="M5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>-74</v>
@@ -720,10 +825,37 @@
       <c r="D6">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>62</v>
+      </c>
+      <c r="F6">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>59</v>
+      </c>
+      <c r="H6">
+        <v>59</v>
+      </c>
+      <c r="I6">
+        <v>59</v>
+      </c>
+      <c r="J6">
+        <v>-74</v>
+      </c>
+      <c r="K6">
+        <v>22</v>
+      </c>
+      <c r="L6">
+        <v>62</v>
+      </c>
+      <c r="M6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>23</v>
@@ -734,32 +866,119 @@
       <c r="D7">
         <v>-24</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>-6</v>
+      </c>
+      <c r="F7">
+        <v>45</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>23</v>
+      </c>
+      <c r="K7">
+        <v>45</v>
+      </c>
+      <c r="L7">
+        <v>-64</v>
+      </c>
+      <c r="M7">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>-30</v>
       </c>
-      <c r="C8" s="4">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>26</v>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>80</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="F8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>-30</v>
+      </c>
+      <c r="H8">
+        <v>76</v>
+      </c>
+      <c r="I8">
+        <v>-79</v>
+      </c>
+      <c r="J8">
+        <v>-79</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>18</v>
+      </c>
+      <c r="M8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>48</v>
+      </c>
+      <c r="H9">
+        <v>48</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>6</v>
+      </c>
+      <c r="L9">
+        <v>50</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -767,10 +986,40 @@
       <c r="C10">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>78</v>
+      </c>
+      <c r="E10">
+        <v>78</v>
+      </c>
+      <c r="F10">
+        <v>78</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>-79</v>
+      </c>
+      <c r="I10">
+        <v>-67</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-6</v>
+      </c>
+      <c r="L10">
+        <v>56</v>
+      </c>
+      <c r="M10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>13</v>
@@ -778,9 +1027,39 @@
       <c r="C11">
         <v>-25</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="D11">
+        <v>15</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>13</v>
+      </c>
+      <c r="I11">
+        <v>13</v>
+      </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
+      <c r="K11">
+        <v>15</v>
+      </c>
+      <c r="L11">
+        <v>-64</v>
+      </c>
+      <c r="M11">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="3">
@@ -789,10 +1068,40 @@
       <c r="C12" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>8</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>9</v>
+      </c>
+      <c r="M12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>-28</v>
@@ -800,10 +1109,40 @@
       <c r="C13">
         <v>42</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>44</v>
+      </c>
+      <c r="E13">
+        <v>44</v>
+      </c>
+      <c r="F13">
+        <v>44</v>
+      </c>
+      <c r="G13">
+        <v>42</v>
+      </c>
+      <c r="H13">
+        <v>42</v>
+      </c>
+      <c r="I13">
+        <v>-28</v>
+      </c>
+      <c r="J13">
+        <v>-28</v>
+      </c>
+      <c r="K13">
+        <v>18</v>
+      </c>
+      <c r="L13">
+        <v>44</v>
+      </c>
+      <c r="M13">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -811,10 +1150,40 @@
       <c r="C14" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="F14">
+        <v>20</v>
+      </c>
+      <c r="G14">
+        <v>-79</v>
+      </c>
+      <c r="H14">
+        <v>-79</v>
+      </c>
+      <c r="I14">
+        <v>17</v>
+      </c>
+      <c r="J14">
+        <v>17</v>
+      </c>
+      <c r="K14">
+        <v>-7</v>
+      </c>
+      <c r="L14">
+        <v>20</v>
+      </c>
+      <c r="M14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -822,15 +1191,75 @@
       <c r="C15" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>15</v>
+      </c>
+      <c r="I15">
+        <v>15</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-9</v>
+      </c>
+      <c r="L15">
+        <v>54</v>
+      </c>
+      <c r="M15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
+        <v>38</v>
+      </c>
+      <c r="D16">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>41</v>
+      </c>
+      <c r="F16">
+        <v>41</v>
+      </c>
+      <c r="G16">
+        <v>38</v>
+      </c>
+      <c r="H16">
+        <v>38</v>
+      </c>
+      <c r="I16">
+        <v>-79</v>
+      </c>
+      <c r="J16">
+        <v>-79</v>
+      </c>
+      <c r="K16">
+        <v>-6</v>
+      </c>
+      <c r="L16">
+        <v>49</v>
+      </c>
+      <c r="M16">
         <v>38</v>
       </c>
     </row>
